--- a/output/Results - sem2.xlsx
+++ b/output/Results - sem2.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="175">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1311" uniqueCount="173">
   <si>
     <t>Rank</t>
   </si>
@@ -307,6 +307,9 @@
     <t>230477</t>
   </si>
   <si>
+    <t>230229</t>
+  </si>
+  <si>
     <t>230180</t>
   </si>
   <si>
@@ -328,9 +331,6 @@
     <t>230012</t>
   </si>
   <si>
-    <t>230229</t>
-  </si>
-  <si>
     <t>230407</t>
   </si>
   <si>
@@ -406,6 +406,9 @@
     <t>230224</t>
   </si>
   <si>
+    <t>230493</t>
+  </si>
+  <si>
     <t>230238</t>
   </si>
   <si>
@@ -418,127 +421,118 @@
     <t>230449</t>
   </si>
   <si>
-    <t>230493</t>
+    <t>1(6.7%)</t>
+  </si>
+  <si>
+    <t>20(17.4%)</t>
+  </si>
+  <si>
+    <t>97(84.3%)</t>
+  </si>
+  <si>
+    <t>23(20.0%)</t>
+  </si>
+  <si>
+    <t>24(20.9%)</t>
+  </si>
+  <si>
+    <t>31(27.0%)</t>
+  </si>
+  <si>
+    <t>73(63.5%)</t>
+  </si>
+  <si>
+    <t>75(65.2%)</t>
+  </si>
+  <si>
+    <t>10(8.7%)</t>
+  </si>
+  <si>
+    <t>11(73.3%)</t>
+  </si>
+  <si>
+    <t>79(68.7%)</t>
+  </si>
+  <si>
+    <t>16(13.9%)</t>
+  </si>
+  <si>
+    <t>51(44.3%)</t>
+  </si>
+  <si>
+    <t>41(35.7%)</t>
+  </si>
+  <si>
+    <t>58(50.4%)</t>
+  </si>
+  <si>
+    <t>37(32.2%)</t>
+  </si>
+  <si>
+    <t>46(40.0%)</t>
+  </si>
+  <si>
+    <t>11(9.6%)</t>
+  </si>
+  <si>
+    <t>1(0.9%)</t>
+  </si>
+  <si>
+    <t>21(18.3%)</t>
+  </si>
+  <si>
+    <t>18(15.7%)</t>
+  </si>
+  <si>
+    <t>9(7.8%)</t>
+  </si>
+  <si>
+    <t>3(2.6%)</t>
+  </si>
+  <si>
+    <t>19(16.5%)</t>
+  </si>
+  <si>
+    <t>2(13.3%)</t>
+  </si>
+  <si>
+    <t>5(4.3%)</t>
+  </si>
+  <si>
+    <t>14(12.2%)</t>
+  </si>
+  <si>
+    <t>17(14.8%)</t>
+  </si>
+  <si>
+    <t>7(6.1%)</t>
+  </si>
+  <si>
+    <t>2(1.7%)</t>
+  </si>
+  <si>
+    <t>0(0.0%)</t>
+  </si>
+  <si>
+    <t>C</t>
+  </si>
+  <si>
+    <t>C-</t>
+  </si>
+  <si>
+    <t>D+</t>
+  </si>
+  <si>
+    <t>D</t>
+  </si>
+  <si>
+    <t>E</t>
+  </si>
+  <si>
+    <t>W</t>
   </si>
   <si>
     <t>I-we</t>
-  </si>
-  <si>
-    <t>1(6.7%)</t>
-  </si>
-  <si>
-    <t>20(17.4%)</t>
-  </si>
-  <si>
-    <t>97(84.3%)</t>
-  </si>
-  <si>
-    <t>23(20.0%)</t>
-  </si>
-  <si>
-    <t>24(20.9%)</t>
-  </si>
-  <si>
-    <t>31(27.0%)</t>
-  </si>
-  <si>
-    <t>73(63.5%)</t>
-  </si>
-  <si>
-    <t>75(65.2%)</t>
-  </si>
-  <si>
-    <t>10(8.7%)</t>
-  </si>
-  <si>
-    <t>11(73.3%)</t>
-  </si>
-  <si>
-    <t>79(68.7%)</t>
-  </si>
-  <si>
-    <t>16(13.9%)</t>
-  </si>
-  <si>
-    <t>50(43.5%)</t>
-  </si>
-  <si>
-    <t>41(35.7%)</t>
-  </si>
-  <si>
-    <t>58(50.4%)</t>
-  </si>
-  <si>
-    <t>37(32.2%)</t>
-  </si>
-  <si>
-    <t>46(40.0%)</t>
-  </si>
-  <si>
-    <t>11(9.6%)</t>
-  </si>
-  <si>
-    <t>1(0.9%)</t>
-  </si>
-  <si>
-    <t>22(19.1%)</t>
-  </si>
-  <si>
-    <t>18(15.7%)</t>
-  </si>
-  <si>
-    <t>9(7.8%)</t>
-  </si>
-  <si>
-    <t>3(2.6%)</t>
-  </si>
-  <si>
-    <t>19(16.5%)</t>
-  </si>
-  <si>
-    <t>2(13.3%)</t>
-  </si>
-  <si>
-    <t>5(4.3%)</t>
-  </si>
-  <si>
-    <t>14(12.2%)</t>
-  </si>
-  <si>
-    <t>17(14.8%)</t>
-  </si>
-  <si>
-    <t>7(6.1%)</t>
-  </si>
-  <si>
-    <t>2(1.7%)</t>
-  </si>
-  <si>
-    <t>0(0.0%)</t>
-  </si>
-  <si>
-    <t>21(18.3%)</t>
-  </si>
-  <si>
-    <t>13(11.3%)</t>
-  </si>
-  <si>
-    <t>C</t>
-  </si>
-  <si>
-    <t>C-</t>
-  </si>
-  <si>
-    <t>D+</t>
-  </si>
-  <si>
-    <t>D</t>
-  </si>
-  <si>
-    <t>E</t>
-  </si>
-  <si>
-    <t>W</t>
   </si>
 </sst>
 </file>
@@ -979,31 +973,31 @@
         <v>14</v>
       </c>
       <c r="P2" t="s">
+        <v>135</v>
+      </c>
+      <c r="Q2" t="s">
         <v>136</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>137</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>138</v>
       </c>
-      <c r="S2" t="s">
+      <c r="T2" t="s">
         <v>139</v>
       </c>
-      <c r="T2" t="s">
+      <c r="U2" t="s">
         <v>140</v>
       </c>
-      <c r="U2" t="s">
+      <c r="V2" t="s">
         <v>141</v>
       </c>
-      <c r="V2" t="s">
+      <c r="W2" t="s">
         <v>142</v>
       </c>
-      <c r="W2" t="s">
+      <c r="X2" t="s">
         <v>143</v>
-      </c>
-      <c r="X2" t="s">
-        <v>144</v>
       </c>
     </row>
     <row r="3" spans="1:24">
@@ -1047,31 +1041,31 @@
         <v>17</v>
       </c>
       <c r="P3" t="s">
+        <v>144</v>
+      </c>
+      <c r="Q3" t="s">
         <v>145</v>
       </c>
-      <c r="Q3" t="s">
+      <c r="R3" t="s">
         <v>146</v>
       </c>
-      <c r="R3" t="s">
+      <c r="S3" t="s">
         <v>147</v>
       </c>
-      <c r="S3" t="s">
+      <c r="T3" t="s">
         <v>148</v>
       </c>
-      <c r="T3" t="s">
+      <c r="U3" t="s">
         <v>149</v>
       </c>
-      <c r="U3" t="s">
+      <c r="V3" t="s">
+        <v>140</v>
+      </c>
+      <c r="W3" t="s">
         <v>150</v>
       </c>
-      <c r="V3" t="s">
-        <v>141</v>
-      </c>
-      <c r="W3" t="s">
+      <c r="X3" t="s">
         <v>151</v>
-      </c>
-      <c r="X3" t="s">
-        <v>152</v>
       </c>
     </row>
     <row r="4" spans="1:24">
@@ -1115,31 +1109,31 @@
         <v>52</v>
       </c>
       <c r="P4" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="Q4" t="s">
+        <v>152</v>
+      </c>
+      <c r="R4" t="s">
         <v>153</v>
       </c>
-      <c r="R4" t="s">
+      <c r="S4" t="s">
         <v>154</v>
       </c>
-      <c r="S4" t="s">
+      <c r="T4" t="s">
+        <v>138</v>
+      </c>
+      <c r="U4" t="s">
         <v>155</v>
       </c>
-      <c r="T4" t="s">
-        <v>139</v>
-      </c>
-      <c r="U4" t="s">
+      <c r="V4" t="s">
         <v>156</v>
       </c>
-      <c r="V4" t="s">
+      <c r="W4" t="s">
         <v>157</v>
       </c>
-      <c r="W4" t="s">
+      <c r="X4" t="s">
         <v>158</v>
-      </c>
-      <c r="X4" t="s">
-        <v>159</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -1183,31 +1177,31 @@
         <v>68</v>
       </c>
       <c r="P5" t="s">
+        <v>159</v>
+      </c>
+      <c r="Q5" t="s">
         <v>160</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="R5" t="s">
+        <v>153</v>
+      </c>
+      <c r="S5" t="s">
         <v>161</v>
       </c>
-      <c r="R5" t="s">
+      <c r="T5" t="s">
+        <v>162</v>
+      </c>
+      <c r="U5" t="s">
+        <v>163</v>
+      </c>
+      <c r="V5" t="s">
+        <v>164</v>
+      </c>
+      <c r="W5" t="s">
+        <v>165</v>
+      </c>
+      <c r="X5" t="s">
         <v>154</v>
-      </c>
-      <c r="S5" t="s">
-        <v>162</v>
-      </c>
-      <c r="T5" t="s">
-        <v>163</v>
-      </c>
-      <c r="U5" t="s">
-        <v>164</v>
-      </c>
-      <c r="V5" t="s">
-        <v>165</v>
-      </c>
-      <c r="W5" t="s">
-        <v>166</v>
-      </c>
-      <c r="X5" t="s">
-        <v>167</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1251,31 +1245,31 @@
         <v>87</v>
       </c>
       <c r="P6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S6" t="s">
+        <v>160</v>
+      </c>
+      <c r="T6" t="s">
+        <v>157</v>
+      </c>
+      <c r="U6" t="s">
+        <v>165</v>
+      </c>
+      <c r="V6" t="s">
+        <v>165</v>
+      </c>
+      <c r="W6" t="s">
+        <v>165</v>
+      </c>
+      <c r="X6" t="s">
         <v>161</v>
-      </c>
-      <c r="T6" t="s">
-        <v>158</v>
-      </c>
-      <c r="U6" t="s">
-        <v>166</v>
-      </c>
-      <c r="V6" t="s">
-        <v>166</v>
-      </c>
-      <c r="W6" t="s">
-        <v>166</v>
-      </c>
-      <c r="X6" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1319,31 +1313,31 @@
         <v>114</v>
       </c>
       <c r="P7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="T7" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="U7" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="V7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W7" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X7" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1387,31 +1381,31 @@
         <v>127</v>
       </c>
       <c r="P8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W8" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X8" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1452,34 +1446,34 @@
         <v>4</v>
       </c>
       <c r="O9" t="s">
-        <v>169</v>
+        <v>166</v>
       </c>
       <c r="P9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X9" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1520,34 +1514,34 @@
         <v>4</v>
       </c>
       <c r="O10" t="s">
-        <v>170</v>
+        <v>167</v>
       </c>
       <c r="P10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X10" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1588,34 +1582,34 @@
         <v>4</v>
       </c>
       <c r="O11" t="s">
-        <v>171</v>
+        <v>168</v>
       </c>
       <c r="P11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X11" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1656,34 +1650,34 @@
         <v>4</v>
       </c>
       <c r="O12" t="s">
-        <v>172</v>
+        <v>169</v>
       </c>
       <c r="P12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X12" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1724,34 +1718,34 @@
         <v>4</v>
       </c>
       <c r="O13" t="s">
-        <v>173</v>
+        <v>170</v>
       </c>
       <c r="P13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X13" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1792,34 +1786,34 @@
         <v>4</v>
       </c>
       <c r="O14" t="s">
-        <v>174</v>
+        <v>171</v>
       </c>
       <c r="P14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X14" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1860,34 +1854,34 @@
         <v>4</v>
       </c>
       <c r="O15" t="s">
-        <v>135</v>
+        <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="Q15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="R15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="S15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="T15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="U15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="V15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="W15" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="X15" t="s">
-        <v>154</v>
+        <v>165</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -4377,10 +4371,10 @@
         <v>14</v>
       </c>
       <c r="F81" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G81" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="H81" t="s">
         <v>17</v>
@@ -4409,16 +4403,16 @@
         <v>13</v>
       </c>
       <c r="D82" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E82" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F82" t="s">
         <v>52</v>
       </c>
       <c r="G82" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H82" t="s">
         <v>17</v>
@@ -4427,10 +4421,10 @@
         <v>17</v>
       </c>
       <c r="J82" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K82" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="L82">
         <v>3.817</v>
@@ -4438,22 +4432,22 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="B83" t="s">
         <v>99</v>
       </c>
       <c r="C83" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D83" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E83" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F83" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G83" t="s">
         <v>68</v>
@@ -4462,16 +4456,16 @@
         <v>17</v>
       </c>
       <c r="I83" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J83" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K83" t="s">
-        <v>87</v>
+        <v>17</v>
       </c>
       <c r="L83">
-        <v>3.811</v>
+        <v>3.817</v>
       </c>
     </row>
     <row r="84" spans="1:12">
@@ -4482,19 +4476,19 @@
         <v>100</v>
       </c>
       <c r="C84" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D84" t="s">
         <v>17</v>
       </c>
       <c r="E84" t="s">
-        <v>68</v>
+        <v>14</v>
       </c>
       <c r="F84" t="s">
         <v>17</v>
       </c>
       <c r="G84" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="H84" t="s">
         <v>17</v>
@@ -4503,13 +4497,13 @@
         <v>14</v>
       </c>
       <c r="J84" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K84" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="L84">
-        <v>3.808</v>
+        <v>3.811</v>
       </c>
     </row>
     <row r="85" spans="1:12">
@@ -4523,31 +4517,31 @@
         <v>13</v>
       </c>
       <c r="D85" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E85" t="s">
-        <v>14</v>
+        <v>68</v>
       </c>
       <c r="F85" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G85" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H85" t="s">
         <v>17</v>
       </c>
       <c r="I85" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="J85" t="s">
         <v>17</v>
       </c>
       <c r="K85" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="L85">
-        <v>3.791</v>
+        <v>3.808</v>
       </c>
     </row>
     <row r="86" spans="1:12">
@@ -4561,31 +4555,31 @@
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E86" t="s">
         <v>14</v>
       </c>
       <c r="F86" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G86" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="H86" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I86" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="J86" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K86" t="s">
         <v>17</v>
       </c>
       <c r="L86">
-        <v>3.786</v>
+        <v>3.791</v>
       </c>
     </row>
     <row r="87" spans="1:12">
@@ -4605,25 +4599,25 @@
         <v>14</v>
       </c>
       <c r="F87" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G87" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="H87" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I87" t="s">
         <v>14</v>
       </c>
       <c r="J87" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K87" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="L87">
-        <v>3.778</v>
+        <v>3.786</v>
       </c>
     </row>
     <row r="88" spans="1:12">
@@ -4643,25 +4637,25 @@
         <v>14</v>
       </c>
       <c r="F88" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>68</v>
+        <v>87</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
       </c>
       <c r="I88" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J88" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K88" t="s">
         <v>68</v>
       </c>
       <c r="L88">
-        <v>3.765</v>
+        <v>3.778</v>
       </c>
     </row>
     <row r="89" spans="1:12">
@@ -5546,34 +5540,34 @@
         <v>130</v>
       </c>
       <c r="C112" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D112" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E112" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F112" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="G112" t="s">
         <v>114</v>
       </c>
       <c r="H112" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="I112" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J112" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="K112" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="L112">
-        <v>3.459</v>
+        <v>3.46</v>
       </c>
     </row>
     <row r="113" spans="1:12">
@@ -5584,34 +5578,34 @@
         <v>131</v>
       </c>
       <c r="C113" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D113" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E113" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F113" t="s">
         <v>87</v>
       </c>
       <c r="G113" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="H113" t="s">
         <v>68</v>
       </c>
       <c r="I113" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="J113" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K113" t="s">
-        <v>87</v>
+        <v>114</v>
       </c>
       <c r="L113">
-        <v>3.456</v>
+        <v>3.459</v>
       </c>
     </row>
     <row r="114" spans="1:12">
@@ -5625,31 +5619,31 @@
         <v>13</v>
       </c>
       <c r="D114" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E114" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F114" t="s">
-        <v>114</v>
+        <v>87</v>
       </c>
       <c r="G114" t="s">
-        <v>114</v>
+        <v>68</v>
       </c>
       <c r="H114" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="I114" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="J114" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K114" t="s">
         <v>87</v>
       </c>
       <c r="L114">
-        <v>3.421</v>
+        <v>3.456</v>
       </c>
     </row>
     <row r="115" spans="1:12">
@@ -5660,34 +5654,34 @@
         <v>133</v>
       </c>
       <c r="C115" t="s">
-        <v>68</v>
+        <v>13</v>
       </c>
       <c r="D115" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="E115" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F115" t="s">
-        <v>68</v>
+        <v>114</v>
       </c>
       <c r="G115" t="s">
         <v>114</v>
       </c>
       <c r="H115" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="I115" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J115" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K115" t="s">
         <v>87</v>
       </c>
       <c r="L115">
-        <v>3.266</v>
+        <v>3.421</v>
       </c>
     </row>
     <row r="116" spans="1:12">
@@ -5698,10 +5692,10 @@
         <v>134</v>
       </c>
       <c r="C116" t="s">
-        <v>13</v>
+        <v>68</v>
       </c>
       <c r="D116" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E116" t="s">
         <v>17</v>
@@ -5713,19 +5707,19 @@
         <v>114</v>
       </c>
       <c r="H116" t="s">
-        <v>52</v>
+        <v>114</v>
       </c>
       <c r="I116" t="s">
         <v>14</v>
       </c>
       <c r="J116" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="K116" t="s">
-        <v>135</v>
+        <v>87</v>
       </c>
       <c r="L116">
-        <v>3.069</v>
+        <v>3.266</v>
       </c>
     </row>
   </sheetData>

--- a/output/Results - sem2.xlsx
+++ b/output/Results - sem2.xlsx
@@ -238,6 +238,9 @@
     <t>230492</t>
   </si>
   <si>
+    <t>230477</t>
+  </si>
+  <si>
     <t>230063</t>
   </si>
   <si>
@@ -304,9 +307,6 @@
     <t>230527</t>
   </si>
   <si>
-    <t>230477</t>
-  </si>
-  <si>
     <t>230229</t>
   </si>
   <si>
@@ -337,6 +337,9 @@
     <t>230261</t>
   </si>
   <si>
+    <t>230650</t>
+  </si>
+  <si>
     <t>230077</t>
   </si>
   <si>
@@ -349,7 +352,7 @@
     <t>230458</t>
   </si>
   <si>
-    <t>230650</t>
+    <t>230327</t>
   </si>
   <si>
     <t>230175</t>
@@ -361,9 +364,6 @@
     <t>B-</t>
   </si>
   <si>
-    <t>230327</t>
-  </si>
-  <si>
     <t>230395</t>
   </si>
   <si>
@@ -451,13 +451,13 @@
     <t>11(73.3%)</t>
   </si>
   <si>
-    <t>79(68.7%)</t>
+    <t>81(70.4%)</t>
   </si>
   <si>
     <t>16(13.9%)</t>
   </si>
   <si>
-    <t>51(44.3%)</t>
+    <t>52(45.2%)</t>
   </si>
   <si>
     <t>41(35.7%)</t>
@@ -472,46 +472,46 @@
     <t>46(40.0%)</t>
   </si>
   <si>
-    <t>11(9.6%)</t>
-  </si>
-  <si>
     <t>1(0.9%)</t>
   </si>
   <si>
+    <t>18(15.7%)</t>
+  </si>
+  <si>
+    <t>9(7.8%)</t>
+  </si>
+  <si>
+    <t>3(2.6%)</t>
+  </si>
+  <si>
+    <t>19(16.5%)</t>
+  </si>
+  <si>
+    <t>2(13.3%)</t>
+  </si>
+  <si>
+    <t>4(3.5%)</t>
+  </si>
+  <si>
+    <t>14(12.2%)</t>
+  </si>
+  <si>
+    <t>17(14.8%)</t>
+  </si>
+  <si>
+    <t>7(6.1%)</t>
+  </si>
+  <si>
+    <t>2(1.7%)</t>
+  </si>
+  <si>
+    <t>0(0.0%)</t>
+  </si>
+  <si>
     <t>21(18.3%)</t>
   </si>
   <si>
-    <t>18(15.7%)</t>
-  </si>
-  <si>
-    <t>9(7.8%)</t>
-  </si>
-  <si>
-    <t>3(2.6%)</t>
-  </si>
-  <si>
-    <t>19(16.5%)</t>
-  </si>
-  <si>
-    <t>2(13.3%)</t>
-  </si>
-  <si>
     <t>5(4.3%)</t>
-  </si>
-  <si>
-    <t>14(12.2%)</t>
-  </si>
-  <si>
-    <t>17(14.8%)</t>
-  </si>
-  <si>
-    <t>7(6.1%)</t>
-  </si>
-  <si>
-    <t>2(1.7%)</t>
-  </si>
-  <si>
-    <t>0(0.0%)</t>
   </si>
   <si>
     <t>C</t>
@@ -1112,28 +1112,28 @@
         <v>135</v>
       </c>
       <c r="Q4" t="s">
+        <v>143</v>
+      </c>
+      <c r="R4" t="s">
         <v>152</v>
       </c>
-      <c r="R4" t="s">
-        <v>153</v>
-      </c>
       <c r="S4" t="s">
-        <v>154</v>
+        <v>136</v>
       </c>
       <c r="T4" t="s">
         <v>138</v>
       </c>
       <c r="U4" t="s">
+        <v>153</v>
+      </c>
+      <c r="V4" t="s">
+        <v>154</v>
+      </c>
+      <c r="W4" t="s">
         <v>155</v>
       </c>
-      <c r="V4" t="s">
+      <c r="X4" t="s">
         <v>156</v>
-      </c>
-      <c r="W4" t="s">
-        <v>157</v>
-      </c>
-      <c r="X4" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="5" spans="1:24">
@@ -1177,31 +1177,31 @@
         <v>68</v>
       </c>
       <c r="P5" t="s">
+        <v>157</v>
+      </c>
+      <c r="Q5" t="s">
+        <v>158</v>
+      </c>
+      <c r="R5" t="s">
+        <v>152</v>
+      </c>
+      <c r="S5" t="s">
         <v>159</v>
       </c>
-      <c r="Q5" t="s">
+      <c r="T5" t="s">
         <v>160</v>
       </c>
-      <c r="R5" t="s">
-        <v>153</v>
-      </c>
-      <c r="S5" t="s">
+      <c r="U5" t="s">
         <v>161</v>
       </c>
-      <c r="T5" t="s">
+      <c r="V5" t="s">
         <v>162</v>
       </c>
-      <c r="U5" t="s">
-        <v>163</v>
-      </c>
-      <c r="V5" t="s">
+      <c r="W5" t="s">
+        <v>163</v>
+      </c>
+      <c r="X5" t="s">
         <v>164</v>
-      </c>
-      <c r="W5" t="s">
-        <v>165</v>
-      </c>
-      <c r="X5" t="s">
-        <v>154</v>
       </c>
     </row>
     <row r="6" spans="1:24">
@@ -1242,34 +1242,34 @@
         <v>4</v>
       </c>
       <c r="O6" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="P6" t="s">
+        <v>163</v>
+      </c>
+      <c r="Q6" t="s">
+        <v>163</v>
+      </c>
+      <c r="R6" t="s">
+        <v>163</v>
+      </c>
+      <c r="S6" t="s">
         <v>165</v>
       </c>
-      <c r="Q6" t="s">
-        <v>165</v>
-      </c>
-      <c r="R6" t="s">
-        <v>165</v>
-      </c>
-      <c r="S6" t="s">
-        <v>160</v>
-      </c>
       <c r="T6" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="U6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W6" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X6" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
     </row>
     <row r="7" spans="1:24">
@@ -1310,34 +1310,34 @@
         <v>4</v>
       </c>
       <c r="O7" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="P7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="T7" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="U7" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="V7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W7" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X7" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
     </row>
     <row r="8" spans="1:24">
@@ -1381,31 +1381,31 @@
         <v>127</v>
       </c>
       <c r="P8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="T8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W8" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X8" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
     </row>
     <row r="9" spans="1:24">
@@ -1449,31 +1449,31 @@
         <v>166</v>
       </c>
       <c r="P9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="T9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X9" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="10" spans="1:24">
@@ -1517,31 +1517,31 @@
         <v>167</v>
       </c>
       <c r="P10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="T10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X10" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="11" spans="1:24">
@@ -1585,31 +1585,31 @@
         <v>168</v>
       </c>
       <c r="P11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="T11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X11" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="12" spans="1:24">
@@ -1653,31 +1653,31 @@
         <v>169</v>
       </c>
       <c r="P12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="T12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X12" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="13" spans="1:24">
@@ -1721,31 +1721,31 @@
         <v>170</v>
       </c>
       <c r="P13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="T13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X13" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="14" spans="1:24">
@@ -1789,31 +1789,31 @@
         <v>171</v>
       </c>
       <c r="P14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="T14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X14" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="15" spans="1:24">
@@ -1857,31 +1857,31 @@
         <v>172</v>
       </c>
       <c r="P15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="Q15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="R15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="S15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="T15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="U15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="V15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="W15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="X15" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
     </row>
     <row r="16" spans="1:24">
@@ -3529,28 +3529,28 @@
         <v>13</v>
       </c>
       <c r="D59" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E59" t="s">
         <v>14</v>
       </c>
       <c r="F59" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="G59" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="H59" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I59" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J59" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K59" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="L59">
         <v>3.908</v>
@@ -3573,22 +3573,22 @@
         <v>14</v>
       </c>
       <c r="F60" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G60" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="H60" t="s">
         <v>17</v>
       </c>
       <c r="I60" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J60" t="s">
         <v>14</v>
       </c>
       <c r="K60" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="L60">
         <v>3.908</v>
@@ -3605,13 +3605,13 @@
         <v>13</v>
       </c>
       <c r="D61" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E61" t="s">
         <v>14</v>
       </c>
       <c r="F61" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G61" t="s">
         <v>17</v>
@@ -3620,13 +3620,13 @@
         <v>17</v>
       </c>
       <c r="I61" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J61" t="s">
         <v>14</v>
       </c>
       <c r="K61" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L61">
         <v>3.908</v>
@@ -3649,10 +3649,10 @@
         <v>14</v>
       </c>
       <c r="F62" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G62" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H62" t="s">
         <v>17</v>
@@ -3664,7 +3664,7 @@
         <v>14</v>
       </c>
       <c r="K62" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="L62">
         <v>3.908</v>
@@ -3687,22 +3687,22 @@
         <v>14</v>
       </c>
       <c r="F63" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="G63" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H63" t="s">
         <v>17</v>
       </c>
       <c r="I63" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J63" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K63" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="L63">
         <v>3.908</v>
@@ -3731,7 +3731,7 @@
         <v>17</v>
       </c>
       <c r="H64" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I64" t="s">
         <v>17</v>
@@ -3740,7 +3740,7 @@
         <v>17</v>
       </c>
       <c r="K64" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="L64">
         <v>3.908</v>
@@ -3786,7 +3786,7 @@
     </row>
     <row r="66" spans="1:12">
       <c r="A66">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="B66" t="s">
         <v>81</v>
@@ -3804,22 +3804,22 @@
         <v>17</v>
       </c>
       <c r="G66" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H66" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I66" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="J66" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K66" t="s">
         <v>52</v>
       </c>
       <c r="L66">
-        <v>3.895</v>
+        <v>3.908</v>
       </c>
     </row>
     <row r="67" spans="1:12">
@@ -3830,7 +3830,7 @@
         <v>82</v>
       </c>
       <c r="C67" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D67" t="s">
         <v>17</v>
@@ -3848,16 +3848,16 @@
         <v>17</v>
       </c>
       <c r="I67" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="J67" t="s">
         <v>14</v>
       </c>
       <c r="K67" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="L67">
-        <v>3.888</v>
+        <v>3.895</v>
       </c>
     </row>
     <row r="68" spans="1:12">
@@ -3868,10 +3868,10 @@
         <v>83</v>
       </c>
       <c r="C68" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D68" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E68" t="s">
         <v>14</v>
@@ -3880,13 +3880,13 @@
         <v>17</v>
       </c>
       <c r="G68" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H68" t="s">
         <v>17</v>
       </c>
       <c r="I68" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="J68" t="s">
         <v>14</v>
@@ -3895,7 +3895,7 @@
         <v>68</v>
       </c>
       <c r="L68">
-        <v>3.882</v>
+        <v>3.888</v>
       </c>
     </row>
     <row r="69" spans="1:12">
@@ -3906,10 +3906,10 @@
         <v>84</v>
       </c>
       <c r="C69" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D69" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E69" t="s">
         <v>14</v>
@@ -3921,19 +3921,19 @@
         <v>17</v>
       </c>
       <c r="H69" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I69" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="J69" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K69" t="s">
         <v>68</v>
       </c>
       <c r="L69">
-        <v>3.877</v>
+        <v>3.882</v>
       </c>
     </row>
     <row r="70" spans="1:12">
@@ -3944,10 +3944,10 @@
         <v>85</v>
       </c>
       <c r="C70" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D70" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E70" t="s">
         <v>14</v>
@@ -3956,10 +3956,10 @@
         <v>17</v>
       </c>
       <c r="G70" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H70" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="I70" t="s">
         <v>14</v>
@@ -3971,12 +3971,12 @@
         <v>68</v>
       </c>
       <c r="L70">
-        <v>3.869</v>
+        <v>3.877</v>
       </c>
     </row>
     <row r="71" spans="1:12">
       <c r="A71">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B71" t="s">
         <v>86</v>
@@ -3985,7 +3985,7 @@
         <v>13</v>
       </c>
       <c r="D71" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E71" t="s">
         <v>14</v>
@@ -3994,7 +3994,7 @@
         <v>17</v>
       </c>
       <c r="G71" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H71" t="s">
         <v>14</v>
@@ -4003,10 +4003,10 @@
         <v>14</v>
       </c>
       <c r="J71" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K71" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="L71">
         <v>3.869</v>
@@ -4014,37 +4014,37 @@
     </row>
     <row r="72" spans="1:12">
       <c r="A72">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B72" t="s">
+        <v>87</v>
+      </c>
+      <c r="C72" t="s">
+        <v>13</v>
+      </c>
+      <c r="D72" t="s">
+        <v>17</v>
+      </c>
+      <c r="E72" t="s">
+        <v>14</v>
+      </c>
+      <c r="F72" t="s">
+        <v>17</v>
+      </c>
+      <c r="G72" t="s">
+        <v>17</v>
+      </c>
+      <c r="H72" t="s">
+        <v>14</v>
+      </c>
+      <c r="I72" t="s">
+        <v>14</v>
+      </c>
+      <c r="J72" t="s">
+        <v>14</v>
+      </c>
+      <c r="K72" t="s">
         <v>88</v>
-      </c>
-      <c r="C72" t="s">
-        <v>13</v>
-      </c>
-      <c r="D72" t="s">
-        <v>14</v>
-      </c>
-      <c r="E72" t="s">
-        <v>14</v>
-      </c>
-      <c r="F72" t="s">
-        <v>17</v>
-      </c>
-      <c r="G72" t="s">
-        <v>68</v>
-      </c>
-      <c r="H72" t="s">
-        <v>17</v>
-      </c>
-      <c r="I72" t="s">
-        <v>14</v>
-      </c>
-      <c r="J72" t="s">
-        <v>14</v>
-      </c>
-      <c r="K72" t="s">
-        <v>52</v>
       </c>
       <c r="L72">
         <v>3.869</v>
@@ -4052,7 +4052,7 @@
     </row>
     <row r="73" spans="1:12">
       <c r="A73">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B73" t="s">
         <v>89</v>
@@ -4061,7 +4061,7 @@
         <v>13</v>
       </c>
       <c r="D73" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="E73" t="s">
         <v>14</v>
@@ -4073,13 +4073,13 @@
         <v>68</v>
       </c>
       <c r="H73" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I73" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J73" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K73" t="s">
         <v>52</v>
@@ -4090,7 +4090,7 @@
     </row>
     <row r="74" spans="1:12">
       <c r="A74">
-        <v>69</v>
+        <v>70</v>
       </c>
       <c r="B74" t="s">
         <v>90</v>
@@ -4105,19 +4105,19 @@
         <v>14</v>
       </c>
       <c r="F74" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="G74" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="H74" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="I74" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J74" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K74" t="s">
         <v>52</v>
@@ -4128,7 +4128,7 @@
     </row>
     <row r="75" spans="1:12">
       <c r="A75">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="B75" t="s">
         <v>91</v>
@@ -4149,19 +4149,19 @@
         <v>52</v>
       </c>
       <c r="H75" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I75" t="s">
         <v>14</v>
       </c>
       <c r="J75" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K75" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="L75">
-        <v>3.856</v>
+        <v>3.869</v>
       </c>
     </row>
     <row r="76" spans="1:12">
@@ -4172,7 +4172,7 @@
         <v>92</v>
       </c>
       <c r="C76" t="s">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="D76" t="s">
         <v>17</v>
@@ -4187,19 +4187,19 @@
         <v>52</v>
       </c>
       <c r="H76" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I76" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J76" t="s">
         <v>17</v>
       </c>
       <c r="K76" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="L76">
-        <v>3.844</v>
+        <v>3.856</v>
       </c>
     </row>
     <row r="77" spans="1:12">
@@ -4210,34 +4210,34 @@
         <v>93</v>
       </c>
       <c r="C77" t="s">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="D77" t="s">
         <v>17</v>
       </c>
       <c r="E77" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F77" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G77" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H77" t="s">
         <v>17</v>
       </c>
       <c r="I77" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J77" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K77" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="L77">
-        <v>3.839</v>
+        <v>3.844</v>
       </c>
     </row>
     <row r="78" spans="1:12">
@@ -4254,13 +4254,13 @@
         <v>17</v>
       </c>
       <c r="E78" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F78" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G78" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="H78" t="s">
         <v>17</v>
@@ -4272,15 +4272,15 @@
         <v>14</v>
       </c>
       <c r="K78" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="L78">
-        <v>3.83</v>
+        <v>3.839</v>
       </c>
     </row>
     <row r="79" spans="1:12">
       <c r="A79">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B79" t="s">
         <v>95</v>
@@ -4310,7 +4310,7 @@
         <v>14</v>
       </c>
       <c r="K79" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L79">
         <v>3.83</v>
@@ -4318,7 +4318,7 @@
     </row>
     <row r="80" spans="1:12">
       <c r="A80">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="B80" t="s">
         <v>96</v>
@@ -4327,36 +4327,36 @@
         <v>13</v>
       </c>
       <c r="D80" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="E80" t="s">
         <v>14</v>
       </c>
       <c r="F80" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="G80" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="H80" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="I80" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J80" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K80" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="L80">
-        <v>3.817</v>
+        <v>3.83</v>
       </c>
     </row>
     <row r="81" spans="1:12">
       <c r="A81">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B81" t="s">
         <v>97</v>
@@ -4394,7 +4394,7 @@
     </row>
     <row r="82" spans="1:12">
       <c r="A82">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B82" t="s">
         <v>98</v>
@@ -4432,7 +4432,7 @@
     </row>
     <row r="83" spans="1:12">
       <c r="A83">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B83" t="s">
         <v>99</v>
@@ -4500,7 +4500,7 @@
         <v>14</v>
       </c>
       <c r="K84" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L84">
         <v>3.811</v>
@@ -4640,7 +4640,7 @@
         <v>17</v>
       </c>
       <c r="G88" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H88" t="s">
         <v>17</v>
@@ -4690,7 +4690,7 @@
         <v>14</v>
       </c>
       <c r="K89" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L89">
         <v>3.756</v>
@@ -4736,40 +4736,40 @@
     </row>
     <row r="91" spans="1:12">
       <c r="A91">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="B91" t="s">
         <v>107</v>
       </c>
       <c r="C91" t="s">
-        <v>52</v>
+        <v>13</v>
       </c>
       <c r="D91" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="E91" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="F91" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="G91" t="s">
         <v>52</v>
       </c>
       <c r="H91" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="I91" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="J91" t="s">
         <v>14</v>
       </c>
       <c r="K91" t="s">
-        <v>87</v>
+        <v>52</v>
       </c>
       <c r="L91">
-        <v>3.733</v>
+        <v>3.747</v>
       </c>
     </row>
     <row r="92" spans="1:12">
@@ -4780,19 +4780,19 @@
         <v>108</v>
       </c>
       <c r="C92" t="s">
-        <v>13</v>
+        <v>52</v>
       </c>
       <c r="D92" t="s">
-        <v>17</v>
+        <v>52</v>
       </c>
       <c r="E92" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="F92" t="s">
         <v>52</v>
       </c>
       <c r="G92" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H92" t="s">
         <v>17</v>
@@ -4804,15 +4804,15 @@
         <v>14</v>
       </c>
       <c r="K92" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L92">
-        <v>3.726</v>
+        <v>3.733</v>
       </c>
     </row>
     <row r="93" spans="1:12">
       <c r="A93">
-        <v>91</v>
+        <v>92</v>
       </c>
       <c r="B93" t="s">
         <v>109</v>
@@ -4830,7 +4830,7 @@
         <v>52</v>
       </c>
       <c r="G93" t="s">
-        <v>87</v>
+        <v>68</v>
       </c>
       <c r="H93" t="s">
         <v>17</v>
@@ -4842,7 +4842,7 @@
         <v>14</v>
       </c>
       <c r="K93" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="L93">
         <v>3.726</v>
@@ -4850,7 +4850,7 @@
     </row>
     <row r="94" spans="1:12">
       <c r="A94">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="B94" t="s">
         <v>110</v>
@@ -4859,7 +4859,7 @@
         <v>13</v>
       </c>
       <c r="D94" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="E94" t="s">
         <v>14</v>
@@ -4868,22 +4868,22 @@
         <v>52</v>
       </c>
       <c r="G94" t="s">
-        <v>68</v>
+        <v>88</v>
       </c>
       <c r="H94" t="s">
-        <v>52</v>
+        <v>17</v>
       </c>
       <c r="I94" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="J94" t="s">
-        <v>17</v>
+        <v>14</v>
       </c>
       <c r="K94" t="s">
         <v>68</v>
       </c>
       <c r="L94">
-        <v>3.713</v>
+        <v>3.726</v>
       </c>
     </row>
     <row r="95" spans="1:12">
@@ -4897,16 +4897,16 @@
         <v>13</v>
       </c>
       <c r="D95" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="E95" t="s">
         <v>14</v>
       </c>
       <c r="F95" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="G95" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="H95" t="s">
         <v>52</v>
@@ -4915,13 +4915,13 @@
         <v>17</v>
       </c>
       <c r="J95" t="s">
-        <v>14</v>
+        <v>17</v>
       </c>
       <c r="K95" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="L95">
-        <v>3.708</v>
+        <v>3.713</v>
       </c>
     </row>
     <row r="96" spans="1:12">
@@ -4941,25 +4941,25 @@
         <v>14</v>
       </c>
       <c r="F96" t="s">
-        <v>68</v>
+        <v>17</v>
       </c>
       <c r="G96" t="s">
         <v>52</v>
       </c>
       <c r="H96" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="I96" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="J96" t="s">
-        <v>52</v>
+        <v>14</v>
       </c>
       <c r="K96" t="s">
-        <v>52</v>
+        <v>88</v>
       </c>
       <c r="L96">
-        <v>3.695</v>
+        <v>3.708</v>
       </c>
     </row>
     <row r="97" spans="1:12">
@@ -4979,25 +4979,25 @@
         <v>14</v>
       </c>
       <c r="F97" t="s">
-        <v>17</v>
+        <v>68</v>
       </c>
       <c r="G97" t="s">
-        <v>68</v>
+        <v>52</v>
       </c>
       <c r="H97" t="s">
         <v>52</v>
       </c>
       <c r="I97" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="J97" t="s">
-        <v>14</v>
+        <v>52</v>
       </c>
       <c r="K97" t="s">
-        <v>114</v>
+        <v>52</v>
       </c>
       <c r="L97">
-        <v>3.686</v>
+        <v>3.695</v>
       </c>
     </row>
     <row r="98" spans="1:12">
@@ -5005,42 +5005,42 @@
         <v>97</v>
       </c>
       <c r="B98" t="s">
+        <v>114</v>
+      </c>
+      <c r="C98" t="s">
+        <v>13</v>
+      </c>
+      <c r="D98" t="s">
+        <v>17</v>
+      </c>
+      <c r="E98" t="s">
+        <v>14</v>
+      </c>
+      <c r="F98" t="s">
+        <v>17</v>
+      </c>
+      <c r="G98" t="s">
+        <v>68</v>
+      </c>
+      <c r="H98" t="s">
+        <v>52</v>
+      </c>
+      <c r="I98" t="s">
+        <v>14</v>
+      </c>
+      <c r="J98" t="s">
+        <v>14</v>
+      </c>
+      <c r="K98" t="s">
         <v>115</v>
       </c>
-      <c r="C98" t="s">
-        <v>13</v>
-      </c>
-      <c r="D98" t="s">
-        <v>17</v>
-      </c>
-      <c r="E98" t="s">
-        <v>14</v>
-      </c>
-      <c r="F98" t="s">
-        <v>52</v>
-      </c>
-      <c r="G98" t="s">
-        <v>52</v>
-      </c>
-      <c r="H98" t="s">
-        <v>68</v>
-      </c>
-      <c r="I98" t="s">
-        <v>14</v>
-      </c>
-      <c r="J98" t="s">
-        <v>14</v>
-      </c>
-      <c r="K98" t="s">
-        <v>87</v>
-      </c>
       <c r="L98">
-        <v>3.656</v>
+        <v>3.686</v>
       </c>
     </row>
     <row r="99" spans="1:12">
       <c r="A99">
-        <v>97</v>
+        <v>98</v>
       </c>
       <c r="B99" t="s">
         <v>116</v>
@@ -5108,7 +5108,7 @@
         <v>17</v>
       </c>
       <c r="K100" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L100">
         <v>3.634</v>
@@ -5146,7 +5146,7 @@
         <v>17</v>
       </c>
       <c r="K101" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L101">
         <v>3.629</v>
@@ -5169,7 +5169,7 @@
         <v>14</v>
       </c>
       <c r="F102" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G102" t="s">
         <v>52</v>
@@ -5207,10 +5207,10 @@
         <v>14</v>
       </c>
       <c r="F103" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G103" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H103" t="s">
         <v>17</v>
@@ -5245,7 +5245,7 @@
         <v>17</v>
       </c>
       <c r="F104" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G104" t="s">
         <v>52</v>
@@ -5298,7 +5298,7 @@
         <v>17</v>
       </c>
       <c r="K105" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L105">
         <v>3.604</v>
@@ -5400,7 +5400,7 @@
         <v>68</v>
       </c>
       <c r="G108" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H108" t="s">
         <v>17</v>
@@ -5438,7 +5438,7 @@
         <v>68</v>
       </c>
       <c r="G109" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H109" t="s">
         <v>52</v>
@@ -5514,7 +5514,7 @@
         <v>68</v>
       </c>
       <c r="G111" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H111" t="s">
         <v>17</v>
@@ -5552,7 +5552,7 @@
         <v>68</v>
       </c>
       <c r="G112" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H112" t="s">
         <v>52</v>
@@ -5564,7 +5564,7 @@
         <v>52</v>
       </c>
       <c r="K112" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L112">
         <v>3.46</v>
@@ -5587,10 +5587,10 @@
         <v>14</v>
       </c>
       <c r="F113" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G113" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H113" t="s">
         <v>68</v>
@@ -5602,7 +5602,7 @@
         <v>14</v>
       </c>
       <c r="K113" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="L113">
         <v>3.459</v>
@@ -5625,7 +5625,7 @@
         <v>17</v>
       </c>
       <c r="F114" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G114" t="s">
         <v>68</v>
@@ -5640,7 +5640,7 @@
         <v>17</v>
       </c>
       <c r="K114" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L114">
         <v>3.456</v>
@@ -5663,10 +5663,10 @@
         <v>14</v>
       </c>
       <c r="F115" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="G115" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H115" t="s">
         <v>52</v>
@@ -5678,7 +5678,7 @@
         <v>14</v>
       </c>
       <c r="K115" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L115">
         <v>3.421</v>
@@ -5704,10 +5704,10 @@
         <v>68</v>
       </c>
       <c r="G116" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="H116" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
       <c r="I116" t="s">
         <v>14</v>
@@ -5716,7 +5716,7 @@
         <v>17</v>
       </c>
       <c r="K116" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="L116">
         <v>3.266</v>
